--- a/excel/Nordstreet.xlsx
+++ b/excel/Nordstreet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.08.08\Nordstreet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3502F2B2-34BD-4A3C-BBEB-D00378A0E280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66BE6D24-AC1F-4541-B116-20069994B5B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3474,7 +3474,7 @@
         <f>'Mesiheina tee 5 ir 8 (1)'!B12</f>
         <v>46140</v>
       </c>
-      <c r="I3" s="24">
+      <c r="I3" s="8">
         <f>'Mesiheina tee 5 ir 8 (1)'!R3</f>
         <v>46140</v>
       </c>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="R3" s="5">
         <f>U3-P3</f>
-        <v>1.3400000000001455</v>
+        <v>9.9100000000000819</v>
       </c>
       <c r="S3" s="5">
         <f>SUM(L3:L200)</f>
@@ -3516,23 +3516,23 @@
       </c>
       <c r="T3" s="5">
         <f>SUM(M3:M200)</f>
-        <v>121.36</v>
+        <v>129.93</v>
       </c>
       <c r="U3" s="5">
         <f>O3+T3+Q3</f>
-        <v>1025.1300000000001</v>
+        <v>1033.7</v>
       </c>
       <c r="V3" s="5">
         <f>U3-O3</f>
-        <v>170.30000000000007</v>
+        <v>178.87</v>
       </c>
       <c r="W3" s="15">
         <f>(U3-O3)/O3</f>
-        <v>0.19922089772235421</v>
+        <v>0.20924628288665581</v>
       </c>
       <c r="X3" s="15">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>0.14719318747520452</v>
+        <v>0.14506028294563295</v>
       </c>
       <c r="AC3" s="5" t="str">
         <f ca="1">'Mesiheina tee 5 ir 8 (1)'!AA2</f>
@@ -3577,11 +3577,11 @@
       </c>
       <c r="J4" s="9">
         <f ca="1">'Bistryčios g. 27 (3)'!B13</f>
-        <v>-53</v>
-      </c>
-      <c r="K4" s="9">
+        <v>-82</v>
+      </c>
+      <c r="K4" s="9" t="str">
         <f ca="1">'Bistryčios g. 27 (3)'!S3</f>
-        <v>53</v>
+        <v/>
       </c>
       <c r="L4" s="5">
         <f>'Bistryčios g. 27 (3)'!N3</f>
@@ -3589,11 +3589,11 @@
       </c>
       <c r="M4" s="5">
         <f>'Bistryčios g. 27 (3)'!P3</f>
-        <v>7.9</v>
+        <v>9.1300000000000008</v>
       </c>
       <c r="AC4" s="5" t="str">
         <f ca="1">'Bistryčios g. 27 (3)'!AA2</f>
-        <v>+</v>
+        <v/>
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.25">
@@ -3634,11 +3634,11 @@
       </c>
       <c r="J5" s="9">
         <f ca="1">'2 MW saulės elektrinių par. (9)'!B13</f>
-        <v>-238</v>
+        <v>-267</v>
       </c>
       <c r="K5" s="9">
         <f ca="1">'2 MW saulės elektrinių par. (9)'!S3</f>
-        <v>361</v>
+        <v>390</v>
       </c>
       <c r="L5" s="5">
         <f>'2 MW saulės elektrinių par. (9)'!N3</f>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="J6" s="9">
         <f ca="1">'Kvartalas "Asiūklės parkas” (2)'!B13</f>
-        <v>173</v>
+        <v>144</v>
       </c>
       <c r="K6" s="9" t="str">
         <f ca="1">'Kvartalas "Asiūklės parkas” (2)'!S3</f>
@@ -3703,7 +3703,7 @@
       </c>
       <c r="M6" s="5">
         <f>'Kvartalas "Asiūklės parkas” (2)'!P3</f>
-        <v>7.7100000000000009</v>
+        <v>8.1700000000000017</v>
       </c>
       <c r="AC6" s="5" t="str">
         <f ca="1">'Kvartalas "Asiūklės parkas” (2)'!AA2</f>
@@ -3976,11 +3976,11 @@
       </c>
       <c r="J11" s="9">
         <f ca="1">'Vidiškių vs., Žemaitkiemio (2)'!B13</f>
-        <v>298</v>
-      </c>
-      <c r="K11" s="9">
+        <v>269</v>
+      </c>
+      <c r="K11" s="9" t="str">
         <f ca="1">'Vidiškių vs., Žemaitkiemio (2)'!S3</f>
-        <v>67</v>
+        <v/>
       </c>
       <c r="L11" s="5">
         <f>'Vidiškių vs., Žemaitkiemio (2)'!N3</f>
@@ -3988,11 +3988,11 @@
       </c>
       <c r="M11" s="5">
         <f>'Vidiškių vs., Žemaitkiemio (2)'!P3</f>
-        <v>8.5100000000000016</v>
+        <v>11.51</v>
       </c>
       <c r="AC11" s="5" t="str">
         <f ca="1">'Vidiškių vs., Žemaitkiemio (2)'!AA2</f>
-        <v>+</v>
+        <v/>
       </c>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.25">
@@ -4090,11 +4090,11 @@
       </c>
       <c r="J13" s="9">
         <f ca="1">'Vilniaus g. 38 38A 38B (1)'!B13</f>
-        <v>-59</v>
+        <v>-88</v>
       </c>
       <c r="K13" s="9">
         <f ca="1">'Vilniaus g. 38 38A 38B (1)'!S3</f>
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="L13" s="5">
         <f>'Vilniaus g. 38 38A 38B (1)'!N3</f>
@@ -4204,11 +4204,11 @@
       </c>
       <c r="J15" s="9">
         <f ca="1">'Viensėdžio g. 36A (3)'!B13</f>
-        <v>-18</v>
+        <v>-47</v>
       </c>
       <c r="K15" s="9">
         <f ca="1">'Viensėdžio g. 36A (3)'!S3</f>
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="L15" s="5">
         <f>'Viensėdžio g. 36A (3)'!N3</f>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="J16" s="9">
         <f ca="1">'Šaltinio g. 7, Panevėžys (1)'!B13</f>
-        <v>372</v>
+        <v>343</v>
       </c>
       <c r="K16" s="9" t="str">
         <f ca="1">'Šaltinio g. 7, Panevėžys (1)'!S3</f>
@@ -4318,11 +4318,11 @@
       </c>
       <c r="J17" s="9">
         <f ca="1">'Mozūriškių g. 17 - 3, Vilnius'!B13</f>
-        <v>18</v>
+        <v>-11</v>
       </c>
       <c r="K17" s="9">
         <f ca="1">'Mozūriškių g. 17 - 3, Vilnius'!S3</f>
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="L17" s="5">
         <f>'Mozūriškių g. 17 - 3, Vilnius'!N3</f>
@@ -4375,11 +4375,11 @@
       </c>
       <c r="J18" s="9">
         <f ca="1">'Parko g. 21 Pergalės g. 36A (1)'!B13</f>
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="K18" s="9">
         <f ca="1">'Parko g. 21 Pergalės g. 36A (1)'!S3</f>
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L18" s="5">
         <f>'Parko g. 21 Pergalės g. 36A (1)'!N3</f>
@@ -4387,7 +4387,7 @@
       </c>
       <c r="M18" s="5">
         <f>'Parko g. 21 Pergalės g. 36A (1)'!P3</f>
-        <v>2.7700000000000005</v>
+        <v>3.4500000000000006</v>
       </c>
       <c r="AC18" s="5" t="str">
         <f ca="1">'Parko g. 21 Pergalės g. 36A (1)'!AA2</f>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="J20" s="9">
         <f ca="1">'Baltų Avenue (1)'!B13</f>
-        <v>443</v>
+        <v>414</v>
       </c>
       <c r="K20" s="9" t="str">
         <f ca="1">'Baltų Avenue (1)'!S3</f>
@@ -4501,7 +4501,7 @@
       </c>
       <c r="M20" s="5">
         <f>'Baltų Avenue (1)'!P3</f>
-        <v>6.2600000000000007</v>
+        <v>6.9700000000000006</v>
       </c>
       <c r="AC20" s="5" t="str">
         <f ca="1">'Baltų Avenue (1)'!AA2</f>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="J21" s="9">
         <f ca="1">'"Filleo Home", Palanga (3)'!B13</f>
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="K21" s="9" t="str">
         <f ca="1">'"Filleo Home", Palanga (3)'!S3</f>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="M21" s="5">
         <f>'"Filleo Home", Palanga (3)'!P3</f>
-        <v>4.6500000000000004</v>
+        <v>5.33</v>
       </c>
       <c r="AC21" s="5" t="str">
         <f ca="1">'"Filleo Home", Palanga (3)'!AA2</f>
@@ -4603,11 +4603,11 @@
       </c>
       <c r="J22" s="9">
         <f ca="1">'Sklypų masyvas Loo, Parnu (1)'!B13</f>
-        <v>181</v>
+        <v>152</v>
       </c>
       <c r="K22" s="9">
         <f ca="1">'Sklypų masyvas Loo, Parnu (1)'!S3</f>
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="L22" s="5">
         <f>'Sklypų masyvas Loo, Parnu (1)'!N3</f>
@@ -4660,11 +4660,11 @@
       </c>
       <c r="J23" s="9">
         <f ca="1">'Liepų g. 3, Vyšniūnai (1)'!B13</f>
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="K23" s="9">
         <f ca="1">'Liepų g. 3, Vyšniūnai (1)'!S3</f>
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="L23" s="5">
         <f>'Liepų g. 3, Vyšniūnai (1)'!N3</f>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="J24" s="9">
         <f ca="1">'Basliupio g. 14, Panevėžys (3)'!B13</f>
-        <v>530</v>
+        <v>501</v>
       </c>
       <c r="K24" s="9" t="str">
         <f ca="1">'Basliupio g. 14, Panevėžys (3)'!S3</f>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="M24" s="5">
         <f>'Basliupio g. 14, Panevėžys (3)'!P3</f>
-        <v>2.96</v>
+        <v>3.56</v>
       </c>
       <c r="AC24" s="5" t="str">
         <f ca="1">'Basliupio g. 14, Panevėžys (3)'!AA2</f>
@@ -4774,11 +4774,11 @@
       </c>
       <c r="J25" s="9">
         <f ca="1">'Mėguvos g. 6 ir 8, Palanga (2)'!B13</f>
-        <v>224</v>
+        <v>195</v>
       </c>
       <c r="K25" s="9">
         <f ca="1">'Mėguvos g. 6 ir 8, Palanga (2)'!S3</f>
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="L25" s="5">
         <f>'Mėguvos g. 6 ir 8, Palanga (2)'!N3</f>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="J26" s="9">
         <f ca="1">'"Filleo Home", Palanga (10)'!B13</f>
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="K26" s="9" t="str">
         <f ca="1">'"Filleo Home", Palanga (10)'!S3</f>
@@ -4843,7 +4843,7 @@
       </c>
       <c r="M26" s="5">
         <f>'"Filleo Home", Palanga (10)'!P3</f>
-        <v>2.25</v>
+        <v>3.01</v>
       </c>
       <c r="AC26" s="5" t="str">
         <f ca="1">'"Filleo Home", Palanga (10)'!AA2</f>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="J27" s="9">
         <f ca="1">'Baltų Avenue (11)'!B13</f>
-        <v>443</v>
+        <v>414</v>
       </c>
       <c r="K27" s="9" t="str">
         <f ca="1">'Baltų Avenue (11)'!S3</f>
@@ -4900,7 +4900,7 @@
       </c>
       <c r="M27" s="5">
         <f>'Baltų Avenue (11)'!P3</f>
-        <v>1.33</v>
+        <v>1.78</v>
       </c>
       <c r="AC27" s="5" t="str">
         <f ca="1">'Baltų Avenue (11)'!AA2</f>
@@ -4945,11 +4945,11 @@
       </c>
       <c r="J28" s="9">
         <f ca="1">'Plento g. 5A, Trakai (2)'!B13</f>
-        <v>295</v>
+        <v>266</v>
       </c>
       <c r="K28" s="9">
         <f ca="1">'Plento g. 5A, Trakai (2)'!S3</f>
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="L28" s="5">
         <f>'Plento g. 5A, Trakai (2)'!N3</f>
@@ -5204,7 +5204,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>4.6500000000000004</v>
+        <v>5.33</v>
       </c>
       <c r="Q3" s="15" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z26,Y2:Y26),"")</f>
@@ -5451,13 +5451,21 @@
       <c r="F9" s="5">
         <v>0.67</v>
       </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0.67</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0.01</v>
+      </c>
+      <c r="J9" s="8">
+        <v>46276</v>
+      </c>
+      <c r="K9" s="9">
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="Y9" s="8">
         <f t="shared" si="1"/>
@@ -5494,11 +5502,11 @@
       </c>
       <c r="Y10" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46276</v>
       </c>
       <c r="Z10" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
@@ -5573,7 +5581,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="D13" s="8">
         <v>46371</v>
@@ -6218,11 +6226,11 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="4"/>
-        <v>4.6500000000000004</v>
+        <v>5.32</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>
@@ -6454,7 +6462,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>6.2600000000000007</v>
+        <v>6.9700000000000006</v>
       </c>
       <c r="Q3" s="15" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z26,Y2:Y26),"")</f>
@@ -6788,13 +6796,21 @@
       <c r="F11" s="5">
         <v>0.71</v>
       </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0.71</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="8">
+        <v>46282</v>
+      </c>
+      <c r="K11" s="9">
+        <f t="shared" si="0"/>
+        <v>-2</v>
       </c>
       <c r="Y11" s="8">
         <f t="shared" si="1"/>
@@ -6832,11 +6848,11 @@
       </c>
       <c r="Y12" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46282</v>
       </c>
       <c r="Z12" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
@@ -6845,7 +6861,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>443</v>
+        <v>414</v>
       </c>
       <c r="D13" s="8">
         <v>46345</v>
@@ -7592,7 +7608,7 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="5"/>
-        <v>6.2600000000000007</v>
+        <v>6.9700000000000006</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="5"/>
@@ -9132,7 +9148,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>2.7700000000000005</v>
+        <v>3.4500000000000006</v>
       </c>
       <c r="Q3" s="15" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z26,Y2:Y26),"")</f>
@@ -9144,7 +9160,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -9298,13 +9314,21 @@
       <c r="F7" s="5">
         <v>0.53</v>
       </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0.53</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="J7" s="8">
+        <v>46282</v>
+      </c>
+      <c r="K7" s="9">
+        <f t="shared" si="0"/>
+        <v>139</v>
       </c>
       <c r="Y7" s="8">
         <f t="shared" si="1"/>
@@ -9342,11 +9366,11 @@
       </c>
       <c r="Y8" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46282</v>
       </c>
       <c r="Z8" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
@@ -9455,7 +9479,7 @@
       <c r="A12" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="8">
         <v>46323</v>
       </c>
       <c r="D12" s="8">
@@ -9491,7 +9515,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="D13" s="8">
         <v>46323</v>
@@ -10136,11 +10160,11 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="5"/>
-        <v>2.7300000000000004</v>
+        <v>3.2600000000000007</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="5"/>
-        <v>0.04</v>
+        <v>0.19</v>
       </c>
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>
@@ -10387,7 +10411,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -10766,7 +10790,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>18</v>
+        <v>-11</v>
       </c>
       <c r="D13" s="8">
         <v>46284</v>
@@ -12048,7 +12072,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>372</v>
+        <v>343</v>
       </c>
       <c r="D13" s="8">
         <v>46273</v>
@@ -12824,6 +12848,9 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13022,7 +13049,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -13411,7 +13438,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>-18</v>
+        <v>-47</v>
       </c>
       <c r="D13" s="8">
         <v>46248</v>
@@ -15504,7 +15531,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -15885,7 +15912,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>-59</v>
+        <v>-88</v>
       </c>
       <c r="D13" s="8">
         <v>46207</v>
@@ -17996,7 +18023,7 @@
       </c>
       <c r="L1" s="15">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>0.14719318747520452</v>
+        <v>0.14506028294563295</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -19822,14 +19849,14 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="8">
         <f ca="1">TODAY()</f>
-        <v>46266</v>
+        <v>46295</v>
       </c>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
       <c r="D200" s="2"/>
       <c r="K200" s="28">
         <f>Apžvalga!U3</f>
-        <v>1025.1300000000001</v>
+        <v>1033.7</v>
       </c>
     </row>
   </sheetData>
@@ -19981,7 +20008,7 @@
       </c>
       <c r="AA2" s="3" t="str">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")&gt;0,"+","")</f>
-        <v>+</v>
+        <v/>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -20030,7 +20057,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>8.5100000000000016</v>
+        <v>11.51</v>
       </c>
       <c r="Q3" s="15" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z26,Y2:Y26),"")</f>
@@ -20040,9 +20067,9 @@
         <f>IF(M3=N3,B14,"")</f>
         <v/>
       </c>
-      <c r="S3" s="3">
+      <c r="S3" s="3" t="str">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>67</v>
+        <v/>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -20431,7 +20458,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>298</v>
+        <v>269</v>
       </c>
       <c r="D13" s="8">
         <v>46199</v>
@@ -20442,13 +20469,21 @@
       <c r="F13" s="5">
         <v>0.7</v>
       </c>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0.11</v>
+      </c>
+      <c r="J13" s="8">
+        <v>46281</v>
+      </c>
+      <c r="K13" s="9">
+        <f t="shared" si="0"/>
+        <v>82</v>
       </c>
       <c r="Y13" s="8">
         <f t="shared" si="1"/>
@@ -20473,21 +20508,29 @@
       <c r="F14" s="5">
         <v>0.67</v>
       </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0.67</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="J14" s="8">
+        <v>46286</v>
+      </c>
+      <c r="K14" s="9">
+        <f t="shared" si="0"/>
+        <v>57</v>
       </c>
       <c r="Y14" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46281</v>
       </c>
       <c r="Z14" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.80999999999999994</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
@@ -20507,21 +20550,29 @@
       <c r="F15" s="5">
         <v>0.7</v>
       </c>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0.04</v>
+      </c>
+      <c r="J15" s="8">
+        <v>46286</v>
+      </c>
+      <c r="K15" s="9">
+        <f t="shared" si="0"/>
+        <v>26</v>
       </c>
       <c r="Y15" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46286</v>
       </c>
       <c r="Z15" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
@@ -20534,21 +20585,29 @@
       <c r="F16" s="5">
         <v>0.7</v>
       </c>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="8">
+        <v>46286</v>
+      </c>
+      <c r="K16" s="9">
+        <f t="shared" si="0"/>
+        <v>-5</v>
       </c>
       <c r="Y16" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46286</v>
       </c>
       <c r="Z16" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="17" spans="4:26" x14ac:dyDescent="0.25">
@@ -20564,18 +20623,18 @@
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
       <c r="I17" s="2"/>
-      <c r="J17" s="3"/>
+      <c r="J17" s="8"/>
       <c r="K17" s="9" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="Y17" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46286</v>
       </c>
       <c r="Z17" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="18" spans="4:26" x14ac:dyDescent="0.25">
@@ -20591,7 +20650,7 @@
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="3"/>
+      <c r="J18" s="8"/>
       <c r="K18" s="9" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -20618,7 +20677,7 @@
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
       <c r="I19" s="2"/>
-      <c r="J19" s="3"/>
+      <c r="J19" s="8"/>
       <c r="K19" s="9" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -20645,7 +20704,7 @@
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
       <c r="I20" s="2"/>
-      <c r="J20" s="3"/>
+      <c r="J20" s="8"/>
       <c r="K20" s="9" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -20672,7 +20731,7 @@
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
       <c r="I21" s="2"/>
-      <c r="J21" s="3"/>
+      <c r="J21" s="8"/>
       <c r="K21" s="9" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -20699,7 +20758,7 @@
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
       <c r="I22" s="2"/>
-      <c r="J22" s="3"/>
+      <c r="J22" s="8"/>
       <c r="K22" s="9" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -20726,7 +20785,7 @@
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
       <c r="I23" s="2"/>
-      <c r="J23" s="3"/>
+      <c r="J23" s="8"/>
       <c r="K23" s="9" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -20753,7 +20812,7 @@
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
       <c r="I24" s="2"/>
-      <c r="J24" s="3"/>
+      <c r="J24" s="8"/>
       <c r="K24" s="9" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -20780,7 +20839,7 @@
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
       <c r="I25" s="2"/>
-      <c r="J25" s="19"/>
+      <c r="J25" s="8"/>
       <c r="K25" s="9" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -21148,11 +21207,11 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="4"/>
-        <v>7.5100000000000007</v>
+        <v>10.28</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>1.2300000000000002</v>
       </c>
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>
@@ -26523,7 +26582,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>7.7100000000000009</v>
+        <v>8.1700000000000017</v>
       </c>
       <c r="Q3" s="15" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z26,Y2:Y26),"")</f>
@@ -26924,7 +26983,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>173</v>
+        <v>144</v>
       </c>
       <c r="D13" s="8">
         <v>46101</v>
@@ -27191,13 +27250,21 @@
       <c r="F20" s="5">
         <v>0.46</v>
       </c>
-      <c r="G20" s="5"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="G20" s="5">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0.46</v>
+      </c>
+      <c r="I20" s="5">
+        <v>0</v>
+      </c>
+      <c r="J20" s="8">
+        <v>46281</v>
+      </c>
+      <c r="K20" s="9">
+        <f t="shared" si="0"/>
+        <v>-4</v>
       </c>
       <c r="Y20" s="8">
         <f t="shared" si="1"/>
@@ -27228,11 +27295,11 @@
       </c>
       <c r="Y21" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46281</v>
       </c>
       <c r="Z21" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="22" spans="4:26" x14ac:dyDescent="0.25">
@@ -27703,7 +27770,7 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="4"/>
-        <v>7.7100000000000009</v>
+        <v>8.1700000000000017</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="4"/>
@@ -27954,7 +28021,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>361</v>
+        <v>390</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -28295,7 +28362,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>-238</v>
+        <v>-267</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="5"/>
@@ -29123,7 +29190,7 @@
       </c>
       <c r="AA2" s="3" t="str">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")&gt;0,"+","")</f>
-        <v>+</v>
+        <v/>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -29168,11 +29235,11 @@
       </c>
       <c r="O3" s="5">
         <f>F42</f>
-        <v>8.08</v>
+        <v>8.57</v>
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>7.9</v>
+        <v>9.1300000000000008</v>
       </c>
       <c r="Q3" s="15" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z26,Y2:Y26),"")</f>
@@ -29182,9 +29249,9 @@
         <f>IF(M3=N3,B14,"")</f>
         <v/>
       </c>
-      <c r="S3" s="3">
+      <c r="S3" s="3" t="str">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>53</v>
+        <v/>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -29573,7 +29640,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>-53</v>
+        <v>-82</v>
       </c>
       <c r="D13" s="8">
         <v>46086</v>
@@ -29762,21 +29829,29 @@
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.25">
       <c r="D18" s="8">
-        <v>46213</v>
+        <v>46275</v>
       </c>
       <c r="E18" s="5">
         <v>50</v>
       </c>
       <c r="F18" s="3">
-        <v>0.18</v>
-      </c>
-      <c r="G18" s="5"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <v>0.67</v>
+      </c>
+      <c r="G18" s="5">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0.67</v>
+      </c>
+      <c r="I18" s="5">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="J18" s="8">
+        <v>46286</v>
+      </c>
+      <c r="K18" s="9">
+        <f t="shared" si="0"/>
+        <v>11</v>
       </c>
       <c r="Y18" s="8">
         <f t="shared" si="1"/>
@@ -29801,11 +29876,11 @@
       </c>
       <c r="Y19" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46286</v>
       </c>
       <c r="Z19" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="20" spans="2:26" x14ac:dyDescent="0.25">
@@ -30281,7 +30356,7 @@
       </c>
       <c r="F42" s="5">
         <f t="shared" ref="F42:I42" si="4">SUM(F2:F41)</f>
-        <v>8.08</v>
+        <v>8.57</v>
       </c>
       <c r="G42" s="5">
         <f t="shared" si="4"/>
@@ -30289,11 +30364,11 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="4"/>
-        <v>7.9</v>
+        <v>8.57</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>
@@ -31662,6 +31737,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47E61392-24B6-482A-9245-A8E55C9F5074}">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+  </sheetPr>
   <dimension ref="A1:AA41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -31844,7 +31922,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -32161,7 +32239,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>295</v>
+        <v>266</v>
       </c>
       <c r="D13" s="8">
         <v>46561</v>
@@ -32893,7 +32971,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>1.33</v>
+        <v>1.78</v>
       </c>
       <c r="Q3" s="15" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z26,Y2:Y26),"")</f>
@@ -32976,13 +33054,21 @@
       <c r="F5" s="5">
         <v>0.45</v>
       </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="8">
+        <v>46272</v>
+      </c>
+      <c r="K5" s="9">
+        <f t="shared" si="0"/>
+        <v>-1</v>
       </c>
       <c r="Y5" s="8">
         <f t="shared" si="1"/>
@@ -33019,11 +33105,11 @@
       </c>
       <c r="Y6" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46272</v>
       </c>
       <c r="Z6" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
@@ -33230,7 +33316,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>443</v>
+        <v>414</v>
       </c>
       <c r="D13" s="8">
         <v>46515</v>
@@ -33935,7 +34021,7 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="4"/>
-        <v>1.33</v>
+        <v>1.78</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="4"/>
@@ -34171,7 +34257,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>2.25</v>
+        <v>3.01</v>
       </c>
       <c r="Q3" s="15" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z26,Y2:Y26),"")</f>
@@ -34254,13 +34340,21 @@
       <c r="F5" s="5">
         <v>0.76</v>
       </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0.76</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="8">
+        <v>46276</v>
+      </c>
+      <c r="K5" s="9">
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="Y5" s="8">
         <f t="shared" si="1"/>
@@ -34297,11 +34391,11 @@
       </c>
       <c r="Y6" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46276</v>
       </c>
       <c r="Z6" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
@@ -34490,7 +34584,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="5"/>
@@ -35129,7 +35223,7 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="4"/>
-        <v>2.25</v>
+        <v>3.01</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="4"/>
@@ -35179,6 +35273,9 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CCADA21-0698-4157-B17D-6AAD26A4F890}">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+  </sheetPr>
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -35377,7 +35474,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -35702,7 +35799,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>224</v>
+        <v>195</v>
       </c>
       <c r="D13" s="8">
         <v>46490</v>
@@ -36583,7 +36680,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>2.96</v>
+        <v>3.56</v>
       </c>
       <c r="Q3" s="15" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z26,Y2:Y26),"")</f>
@@ -36710,7 +36807,7 @@
       <c r="G6" s="5">
         <v>0</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="5">
         <v>0.6</v>
       </c>
       <c r="I6" s="5">
@@ -36748,13 +36845,21 @@
       <c r="F7" s="5">
         <v>0.6</v>
       </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="8">
+        <v>46274</v>
+      </c>
+      <c r="K7" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="Y7" s="8">
         <f t="shared" si="1"/>
@@ -36791,11 +36896,11 @@
       </c>
       <c r="Y8" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46274</v>
       </c>
       <c r="Z8" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
@@ -36936,7 +37041,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>530</v>
+        <v>501</v>
       </c>
       <c r="D13" s="8">
         <v>46455</v>
@@ -37653,7 +37758,7 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="4"/>
-        <v>2.96</v>
+        <v>3.56</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="4"/>
@@ -37904,7 +38009,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -38237,7 +38342,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="D13" s="8">
         <v>46429</v>
@@ -39133,7 +39238,7 @@
       </c>
       <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
@@ -39482,7 +39587,7 @@
       </c>
       <c r="B13" s="9">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>181</v>
+        <v>152</v>
       </c>
       <c r="D13" s="8">
         <v>46394</v>
